--- a/firmware/SDRAM_Table.xlsx
+++ b/firmware/SDRAM_Table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aweso\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D538E34E-AF17-402B-90CC-90AE5678E5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6ADA11-904D-4B20-9CA7-A73E4DE612E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5460" yWindow="1965" windowWidth="21600" windowHeight="11385" xr2:uid="{2EE69FAC-92AE-4D51-8137-EDC6C5E3C988}"/>
   </bookViews>
@@ -68,13 +68,13 @@
     <t>15ns (2 cycles)</t>
   </si>
   <si>
-    <t>60ns (6 cycles)</t>
-  </si>
-  <si>
     <t>2 cycles</t>
   </si>
   <si>
     <t>7.81us (781 cycles)</t>
+  </si>
+  <si>
+    <t>66ns (7 cycles)</t>
   </si>
 </sst>
 </file>
@@ -466,7 +466,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -482,7 +482,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -506,7 +506,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
